--- a/data/trans_orig/P1419-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2007</t>
+          <t>Población con diagnóstico de varices en las piernas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27781</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51821</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255935</t>
+          <t>255282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267530</t>
+          <t>267575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220389</t>
+          <t>220364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241755</t>
+          <t>241204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482027</t>
+          <t>481880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>506067</t>
+          <t>507225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30712</t>
+          <t>31713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40816</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>67723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57356</t>
+          <t>57784</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89608</t>
+          <t>90377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462363</t>
+          <t>461362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481676</t>
+          <t>481424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436147</t>
+          <t>436226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463133</t>
+          <t>463447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907416</t>
+          <t>906647</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939668</t>
+          <t>939240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>12045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309995</t>
+          <t>308848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317896</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306307</t>
+          <t>306382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323345</t>
+          <t>323367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621234</t>
+          <t>618215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640146</t>
+          <t>639129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34263</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58894</t>
+          <t>58301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38972</t>
+          <t>39656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65852</t>
+          <t>65083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344904</t>
+          <t>345208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356127</t>
+          <t>356152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>312562</t>
+          <t>313155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337193</t>
+          <t>337177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>664275</t>
+          <t>665044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>691155</t>
+          <t>690471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24014</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28735</t>
+          <t>29912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194722</t>
+          <t>195134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202437</t>
+          <t>202435</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183654</t>
+          <t>183281</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199434</t>
+          <t>199125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>382241</t>
+          <t>381064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>400219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23895</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>45666</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26870</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>51172</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258191</t>
+          <t>257773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232181</t>
+          <t>232478</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254249</t>
+          <t>255401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497715</t>
+          <t>497783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>522085</t>
+          <t>521669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18140</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39879</t>
+          <t>39724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66352</t>
+          <t>66331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>47790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78960</t>
+          <t>77499</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596887</t>
+          <t>596785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610656</t>
+          <t>610729</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>571867</t>
+          <t>571888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>598340</t>
+          <t>598495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1174286</t>
+          <t>1175747</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1204922</t>
+          <t>1205456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31498</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56629</t>
+          <t>56717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>98501</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>137781</t>
+          <t>135157</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138187</t>
+          <t>138115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189026</t>
+          <t>183954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>687166</t>
+          <t>687078</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>712297</t>
+          <t>711575</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>645730</t>
+          <t>648354</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>686006</t>
+          <t>685010</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1338280</t>
+          <t>1343352</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1389119</t>
+          <t>1389191</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>80228</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>118709</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>331117</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>402469</t>
+          <t>402712</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>422231</t>
+          <t>424119</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>507266</t>
+          <t>505612</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3157834</t>
+          <t>3157309</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3194502</t>
+          <t>3196315</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2976728</t>
+          <t>2976485</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3049580</t>
+          <t>3048080</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6148475</t>
+          <t>6150129</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6233510</t>
+          <t>6231622</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2012</t>
+          <t>Población con diagnóstico de varices en las piernas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25145</t>
+          <t>25305</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29823</t>
+          <t>28237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286750</t>
+          <t>286422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262100</t>
+          <t>261940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278957</t>
+          <t>278683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>552160</t>
+          <t>553746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>571927</t>
+          <t>572495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26305</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53689</t>
+          <t>51932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489813</t>
+          <t>489189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502493</t>
+          <t>502502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479157</t>
+          <t>479706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502272</t>
+          <t>503701</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975603</t>
+          <t>977360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002987</t>
+          <t>1002911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>22977</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28175</t>
+          <t>28984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313712</t>
+          <t>314495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323016</t>
+          <t>323009</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318018</t>
+          <t>318043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333622</t>
+          <t>332448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636891</t>
+          <t>636082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653630</t>
+          <t>653515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>34872</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60860</t>
+          <t>61581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38026</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66197</t>
+          <t>67233</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360522</t>
+          <t>360904</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373012</t>
+          <t>373009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328091</t>
+          <t>327370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354803</t>
+          <t>354079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696736</t>
+          <t>695700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724907</t>
+          <t>724944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26872</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48722</t>
+          <t>48599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>32288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56220</t>
+          <t>56784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201611</t>
+          <t>200821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210624</t>
+          <t>210593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170869</t>
+          <t>170992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192719</t>
+          <t>192557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375989</t>
+          <t>375425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400489</t>
+          <t>399921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>32421</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>17239</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265494</t>
+          <t>265013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273043</t>
+          <t>273035</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245536</t>
+          <t>245675</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263077</t>
+          <t>263767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516128</t>
+          <t>516110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>535481</t>
+          <t>534838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53088</t>
+          <t>53588</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86474</t>
+          <t>87065</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59385</t>
+          <t>61132</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95225</t>
+          <t>96315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645919</t>
+          <t>648066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660691</t>
+          <t>660766</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607379</t>
+          <t>606788</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>640765</t>
+          <t>640265</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1261416</t>
+          <t>1260326</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1297256</t>
+          <t>1295509</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48277</t>
+          <t>48229</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80307</t>
+          <t>81318</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54920</t>
+          <t>56403</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89102</t>
+          <t>89724</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762607</t>
+          <t>763408</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774971</t>
+          <t>775017</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>742271</t>
+          <t>741260</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>774301</t>
+          <t>774349</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1512574</t>
+          <t>1511952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1546756</t>
+          <t>1545273</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>264972</t>
+          <t>268434</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>330767</t>
+          <t>337083</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>300661</t>
+          <t>301477</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>377543</t>
+          <t>376641</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3370587</t>
+          <t>3370687</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3396994</t>
+          <t>3398568</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3224331</t>
+          <t>3218015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3290126</t>
+          <t>3286664</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6604334</t>
+          <t>6605236</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6681216</t>
+          <t>6680400</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2016</t>
+          <t>Población con diagnóstico de varices en las piernas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30555</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283918</t>
+          <t>281820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292883</t>
+          <t>292881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258148</t>
+          <t>258305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276021</t>
+          <t>276731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547409</t>
+          <t>547199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>566787</t>
+          <t>567675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21297</t>
+          <t>23022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>23218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496832</t>
+          <t>496816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501787</t>
+          <t>500062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518099</t>
+          <t>517216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002761</t>
+          <t>1002441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019262</t>
+          <t>1019258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>55777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33474</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>58915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308070</t>
+          <t>307993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316778</t>
+          <t>316763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283330</t>
+          <t>280532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>308908</t>
+          <t>307034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592643</t>
+          <t>595959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621400</t>
+          <t>623322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43592</t>
+          <t>43376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>49489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356326</t>
+          <t>356260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367175</t>
+          <t>367188</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343691</t>
+          <t>343907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366939</t>
+          <t>367498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706386</t>
+          <t>707758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>733196</t>
+          <t>732886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201522</t>
+          <t>202205</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210213</t>
+          <t>210224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>205839</t>
+          <t>204873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215758</t>
+          <t>215605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410796</t>
+          <t>411358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424077</t>
+          <t>424041</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8828</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24823</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27885</t>
+          <t>27862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254807</t>
+          <t>254295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262337</t>
+          <t>262332</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248292</t>
+          <t>248132</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265024</t>
+          <t>265399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>508353</t>
+          <t>508376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525763</t>
+          <t>526913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>23884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26290</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52880</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>40334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69873</t>
+          <t>72475</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>633083</t>
+          <t>632674</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648372</t>
+          <t>648342</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638414</t>
+          <t>638261</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>665004</t>
+          <t>664596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1277979</t>
+          <t>1275377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1307314</t>
+          <t>1307518</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41552</t>
+          <t>43817</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72714</t>
+          <t>76076</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>54983</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93114</t>
+          <t>89377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>754266</t>
+          <t>754738</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>769848</t>
+          <t>770097</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>753453</t>
+          <t>750091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>784615</t>
+          <t>782350</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1511636</t>
+          <t>1515373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1548306</t>
+          <t>1549767</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39669</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>66907</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>190504</t>
+          <t>187489</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>250283</t>
+          <t>251019</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238736</t>
+          <t>238950</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>304018</t>
+          <t>307574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3325367</t>
+          <t>3327443</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3354681</t>
+          <t>3354627</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3294259</t>
+          <t>3293523</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3354038</t>
+          <t>3357053</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6634874</t>
+          <t>6631318</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6700156</t>
+          <t>6699942</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2023</t>
+          <t>Población con diagnóstico de varices en las piernas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304312</t>
+          <t>304134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310700</t>
+          <t>310694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280628</t>
+          <t>280451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287206</t>
+          <t>287007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587875</t>
+          <t>587817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596919</t>
+          <t>596892</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42259</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64926</t>
+          <t>65361</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55237</t>
+          <t>54479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>83369</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492813</t>
+          <t>493195</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508975</t>
+          <t>508518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448641</t>
+          <t>448206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>471308</t>
+          <t>471463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>948303</t>
+          <t>947591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>975723</t>
+          <t>976481</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>20022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>35925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>30655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>51714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296431</t>
+          <t>296028</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308829</t>
+          <t>308522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>312614</t>
+          <t>313203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>327918</t>
+          <t>328180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613028</t>
+          <t>613464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633184</t>
+          <t>634523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35577</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21974</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44287</t>
+          <t>42798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297645</t>
+          <t>298266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309839</t>
+          <t>310051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440141</t>
+          <t>440238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460937</t>
+          <t>460728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743987</t>
+          <t>745476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766300</t>
+          <t>766061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>17368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35682</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>50904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64007</t>
+          <t>63897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,51%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160555</t>
+          <t>161374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171339</t>
+          <t>171637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157874</t>
+          <t>157370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172592</t>
+          <t>171949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323009</t>
+          <t>323119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340753</t>
+          <t>341757</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>30250</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45498</t>
+          <t>45619</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39228</t>
+          <t>40028</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58413</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253364</t>
+          <t>252979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263073</t>
+          <t>262990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210889</t>
+          <t>210768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>225804</t>
+          <t>226137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>467610</t>
+          <t>467277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>486795</t>
+          <t>485995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>40468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66532</t>
+          <t>67284</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>70852</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>194623</t>
+          <t>195460</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121261</t>
+          <t>121189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232620</t>
+          <t>236620</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>557028</t>
+          <t>556276</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583136</t>
+          <t>583092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>654482</t>
+          <t>653645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>782081</t>
+          <t>778253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1240045</t>
+          <t>1236045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351404</t>
+          <t>1351476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24971</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43205</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>28227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57396</t>
+          <t>59167</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>909745</t>
+          <t>908936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>925012</t>
+          <t>924514</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>672187</t>
+          <t>671985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>690421</t>
+          <t>689978</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1586716</t>
+          <t>1584945</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1617975</t>
+          <t>1615885</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94642</t>
+          <t>93768</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>145440</t>
+          <t>145705</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>303230</t>
+          <t>301167</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>405612</t>
+          <t>407814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>427074</t>
+          <t>428811</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>534207</t>
+          <t>538558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3312661</t>
+          <t>3312396</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3363459</t>
+          <t>3364333</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3251592</t>
+          <t>3249390</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3353974</t>
+          <t>3356037</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6581099</t>
+          <t>6576748</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6688232</t>
+          <t>6686495</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1419-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>27553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51968</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255282</t>
+          <t>255235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267575</t>
+          <t>267498</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220364</t>
+          <t>220735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241204</t>
+          <t>241751</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>481880</t>
+          <t>482449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>507225</t>
+          <t>506295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>10881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31713</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40502</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67723</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57784</t>
+          <t>56948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90377</t>
+          <t>91168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461362</t>
+          <t>462270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481424</t>
+          <t>482194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436226</t>
+          <t>436050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463447</t>
+          <t>463655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906647</t>
+          <t>905856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>939240</t>
+          <t>940076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29030</t>
+          <t>31079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36043</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308848</t>
+          <t>310782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317899</t>
+          <t>317900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>306382</t>
+          <t>304333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323367</t>
+          <t>322624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>618215</t>
+          <t>621220</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639129</t>
+          <t>640154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13463</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>34508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58301</t>
+          <t>58707</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39656</t>
+          <t>39235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65083</t>
+          <t>65790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345208</t>
+          <t>343910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356152</t>
+          <t>356135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>313155</t>
+          <t>312749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337177</t>
+          <t>336948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665044</t>
+          <t>664337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>690471</t>
+          <t>690892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8844</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10757</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>27922</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195134</t>
+          <t>194528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202435</t>
+          <t>202427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183281</t>
+          <t>182712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199125</t>
+          <t>198824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>381064</t>
+          <t>383054</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400219</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>12933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22743</t>
+          <t>24016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51172</t>
+          <t>50477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257773</t>
+          <t>257878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269746</t>
+          <t>269099</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232478</t>
+          <t>232113</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255401</t>
+          <t>254128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497783</t>
+          <t>498478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521669</t>
+          <t>521972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39724</t>
+          <t>39828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66331</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47790</t>
+          <t>47710</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77499</t>
+          <t>78068</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596785</t>
+          <t>597866</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610729</t>
+          <t>610638</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>571888</t>
+          <t>570958</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>598495</t>
+          <t>598391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1175747</t>
+          <t>1175178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1205456</t>
+          <t>1205536</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32220</t>
+          <t>31538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56717</t>
+          <t>57559</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98501</t>
+          <t>97042</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>135157</t>
+          <t>138802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138115</t>
+          <t>137013</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183954</t>
+          <t>183806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>687078</t>
+          <t>686236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>711575</t>
+          <t>712257</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>648354</t>
+          <t>644709</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>685010</t>
+          <t>686469</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1343352</t>
+          <t>1343500</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1389191</t>
+          <t>1390293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>79996</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>119234</t>
+          <t>120579</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>331117</t>
+          <t>326983</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>402712</t>
+          <t>400540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>424119</t>
+          <t>419464</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>505612</t>
+          <t>503578</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3157309</t>
+          <t>3155964</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3196315</t>
+          <t>3196547</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2976485</t>
+          <t>2978657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3048080</t>
+          <t>3052214</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6150129</t>
+          <t>6152163</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6231622</t>
+          <t>6236277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>7714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25305</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28237</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286422</t>
+          <t>287024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261940</t>
+          <t>259749</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278683</t>
+          <t>278612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553746</t>
+          <t>553178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>572495</t>
+          <t>572139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16338</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20064</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44059</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26381</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51932</t>
+          <t>51641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489189</t>
+          <t>490004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502502</t>
+          <t>502561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>479706</t>
+          <t>480556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503701</t>
+          <t>502993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>977360</t>
+          <t>977651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002911</t>
+          <t>1002667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11551</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>29935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314495</t>
+          <t>314641</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323009</t>
+          <t>323018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318043</t>
+          <t>317900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332448</t>
+          <t>332838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636082</t>
+          <t>635131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653515</t>
+          <t>653440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34872</t>
+          <t>34214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61581</t>
+          <t>62477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37989</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67233</t>
+          <t>66932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360904</t>
+          <t>361611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373009</t>
+          <t>373016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327370</t>
+          <t>326474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354079</t>
+          <t>354737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695700</t>
+          <t>696001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>724944</t>
+          <t>725548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27034</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48599</t>
+          <t>48633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>30874</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56784</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200821</t>
+          <t>201591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210593</t>
+          <t>210801</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170992</t>
+          <t>170958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192557</t>
+          <t>192254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375425</t>
+          <t>375010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399921</t>
+          <t>401335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32421</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35967</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>265013</t>
+          <t>265875</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273035</t>
+          <t>273043</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245675</t>
+          <t>245757</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>263767</t>
+          <t>263890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516110</t>
+          <t>513892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>534838</t>
+          <t>535174</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53588</t>
+          <t>54684</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>87065</t>
+          <t>88512</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61132</t>
+          <t>60985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96315</t>
+          <t>97815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648066</t>
+          <t>647782</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660766</t>
+          <t>660756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606788</t>
+          <t>605341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>640265</t>
+          <t>639169</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1260326</t>
+          <t>1258826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1295509</t>
+          <t>1295656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48229</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81318</t>
+          <t>79850</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>54846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>89313</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763408</t>
+          <t>763316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775017</t>
+          <t>775026</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>741260</t>
+          <t>742728</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>774349</t>
+          <t>772983</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1511952</t>
+          <t>1512363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1545273</t>
+          <t>1546830</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56092</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>268434</t>
+          <t>268396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>337083</t>
+          <t>331839</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>301477</t>
+          <t>306249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>376641</t>
+          <t>379222</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3370687</t>
+          <t>3369621</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3398568</t>
+          <t>3397756</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3218015</t>
+          <t>3223259</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3286664</t>
+          <t>3286702</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6605236</t>
+          <t>6602655</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6680400</t>
+          <t>6675628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11941</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>31288</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35265</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>281820</t>
+          <t>282663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292881</t>
+          <t>292884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258305</t>
+          <t>257415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276731</t>
+          <t>275709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>547199</t>
+          <t>545886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>567675</t>
+          <t>567153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496816</t>
+          <t>496258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500062</t>
+          <t>502172</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>517216</t>
+          <t>517502</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002441</t>
+          <t>1003143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019258</t>
+          <t>1019489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29275</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55777</t>
+          <t>54089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31552</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58915</t>
+          <t>60681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307993</t>
+          <t>307552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316763</t>
+          <t>316709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>280532</t>
+          <t>282220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307034</t>
+          <t>307506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>595959</t>
+          <t>594193</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623322</t>
+          <t>621837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49489</t>
+          <t>51048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356260</t>
+          <t>356072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367188</t>
+          <t>367383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343907</t>
+          <t>343624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367498</t>
+          <t>367977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707758</t>
+          <t>706199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>732886</t>
+          <t>732695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>19068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202205</t>
+          <t>202194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210224</t>
+          <t>210228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204873</t>
+          <t>205486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215605</t>
+          <t>215655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>411358</t>
+          <t>410740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424041</t>
+          <t>424142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8828</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>23300</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27862</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254295</t>
+          <t>254919</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262332</t>
+          <t>262335</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248132</t>
+          <t>249815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265399</t>
+          <t>265723</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>508376</t>
+          <t>507645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>526913</t>
+          <t>525480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>7923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>23464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>27360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53033</t>
+          <t>52912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40334</t>
+          <t>40141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>632674</t>
+          <t>633094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>648342</t>
+          <t>648635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>638261</t>
+          <t>638382</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>664596</t>
+          <t>663934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1275377</t>
+          <t>1278835</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1307518</t>
+          <t>1307711</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43817</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76076</t>
+          <t>74853</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54983</t>
+          <t>56348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>89377</t>
+          <t>91448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>754738</t>
+          <t>753530</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>770097</t>
+          <t>769673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>750091</t>
+          <t>751314</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>782350</t>
+          <t>782796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1515373</t>
+          <t>1513302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1549767</t>
+          <t>1548402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66907</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187489</t>
+          <t>189281</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>251019</t>
+          <t>249845</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>238950</t>
+          <t>235967</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>305143</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3327443</t>
+          <t>3324768</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3354627</t>
+          <t>3355209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3293523</t>
+          <t>3294697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3357053</t>
+          <t>3355261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6631318</t>
+          <t>6633749</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6699942</t>
+          <t>6702925</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308846</t>
+          <t>315911</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304134</t>
+          <t>311845</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>318141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>284638</t>
+          <t>310399</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280451</t>
+          <t>305651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287007</t>
+          <t>313102</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>593483</t>
+          <t>626310</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587817</t>
+          <t>620699</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596892</t>
+          <t>630067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>44546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65361</t>
+          <t>67916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67637</t>
+          <t>70934</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54479</t>
+          <t>57727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83369</t>
+          <t>87036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>502379</t>
+          <t>514207</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493195</t>
+          <t>504139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>508518</t>
+          <t>521202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>460944</t>
+          <t>489625</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448206</t>
+          <t>477190</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>471463</t>
+          <t>500560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>963323</t>
+          <t>1003832</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947591</t>
+          <t>987730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976481</t>
+          <t>1017039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513567</t>
+          <t>545106</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513567</t>
+          <t>545106</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513567</t>
+          <t>545106</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030960</t>
+          <t>1074766</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030960</t>
+          <t>1074766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030960</t>
+          <t>1074766</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27936</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35925</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40379</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30655</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51714</t>
+          <t>53150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>303606</t>
+          <t>303648</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296028</t>
+          <t>296088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308522</t>
+          <t>308449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>321192</t>
+          <t>326802</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313203</t>
+          <t>318026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328180</t>
+          <t>334033</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>624799</t>
+          <t>630452</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613464</t>
+          <t>619225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634523</t>
+          <t>639372</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14291</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>27064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>47793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>306092</t>
+          <t>364661</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298266</t>
+          <t>355558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310051</t>
+          <t>369456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>450323</t>
+          <t>394160</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>440238</t>
+          <t>385773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>460728</t>
+          <t>400939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>756414</t>
+          <t>758821</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>745476</t>
+          <t>747314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>766061</t>
+          <t>768043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>19090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>44124</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36325</t>
+          <t>37094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50904</t>
+          <t>52340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45259</t>
+          <t>47312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63897</t>
+          <t>66960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>167153</t>
+          <t>192735</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>161374</t>
+          <t>186575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171637</t>
+          <t>197549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>165218</t>
+          <t>182699</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157370</t>
+          <t>174483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171949</t>
+          <t>189729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>332370</t>
+          <t>375434</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323119</t>
+          <t>365528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341757</t>
+          <t>385176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30250</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45619</t>
+          <t>46138</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>47877</t>
+          <t>48966</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40028</t>
+          <t>39910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259135</t>
+          <t>259954</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252979</t>
+          <t>254221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262990</t>
+          <t>263786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>219011</t>
+          <t>224886</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>210768</t>
+          <t>216961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226137</t>
+          <t>232514</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>478146</t>
+          <t>484840</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>467277</t>
+          <t>475139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>485995</t>
+          <t>493896</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>52513</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67284</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>141848</t>
+          <t>167455</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70852</t>
+          <t>150844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195460</t>
+          <t>189491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>194361</t>
+          <t>227767</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121189</t>
+          <t>201638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>236620</t>
+          <t>253259</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>571047</t>
+          <t>658507</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556276</t>
+          <t>643262</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>583092</t>
+          <t>673101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>707257</t>
+          <t>603919</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>653645</t>
+          <t>581883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>778253</t>
+          <t>620530</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1278304</t>
+          <t>1262426</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1236045</t>
+          <t>1236934</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351476</t>
+          <t>1288555</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623560</t>
+          <t>718819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849105</t>
+          <t>771374</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849105</t>
+          <t>771374</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849105</t>
+          <t>771374</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472665</t>
+          <t>1490193</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472665</t>
+          <t>1490193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472665</t>
+          <t>1490193</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19784</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>38634</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>59167</t>
+          <t>62757</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>917969</t>
+          <t>786025</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>908936</t>
+          <t>778074</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>924514</t>
+          <t>791306</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>682247</t>
+          <t>792587</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>671985</t>
+          <t>780695</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>689978</t>
+          <t>801370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1600216</t>
+          <t>1578612</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1584945</t>
+          <t>1565924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1615885</t>
+          <t>1590047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>93768</t>
+          <t>115239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>145705</t>
+          <t>157044</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>366375</t>
+          <t>406336</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>301167</t>
+          <t>379438</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>407814</t>
+          <t>439184</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>488249</t>
+          <t>541595</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>428811</t>
+          <t>501568</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>538558</t>
+          <t>578599</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3336227</t>
+          <t>3395647</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3312396</t>
+          <t>3373862</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3364333</t>
+          <t>3415667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3290829</t>
+          <t>3325079</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3249390</t>
+          <t>3292231</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3356037</t>
+          <t>3351977</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6627057</t>
+          <t>6720727</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6576748</t>
+          <t>6683723</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6686495</t>
+          <t>6760754</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
